--- a/public/templates/Nhap_khau_hang_hoa_MISA.xlsx
+++ b/public/templates/Nhap_khau_hang_hoa_MISA.xlsx
@@ -21,9 +21,6 @@
     <sheet name="Brands" sheetId="6" state="hidden" r:id="rId6"/>
     <sheet name="Attributes" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
   <definedNames>
     <definedName name="SAVoucher">'Tep nhap khau'!#REF!</definedName>
   </definedNames>
@@ -1833,22 +1830,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="danh mục"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -3119,35 +3100,6 @@
           <xm:sqref>J6:J40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="64" id="{00000000-000E-0000-0100-000040000000}">
-            <xm:f>OR($C41='\Downloads\[1]danh mục'!#REF!,$C41='\Downloads\[1]danh mục'!#REF!)</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFA6A6A6"/>
-                </patternFill>
-              </fill>
-              <border>
-                <left/>
-                <right/>
-                <top/>
-                <bottom/>
-              </border>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="63" id="{00000000-000E-0000-0100-00003F000000}">
-            <xm:f>OR($C41='\Downloads\[1]danh mục'!#REF!,$C41='\Downloads\[1]danh mục'!#REF!)</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFB9CDE5"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>J41:J1387</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="46" id="{00000000-000E-0000-0100-00002E000000}">
             <xm:f>OR($C7='Danh mục'!$B$4,$C7='Danh mục'!$B$5)</xm:f>
             <x14:dxf>
